--- a/Result/checksun_type/擴散膜、增亮膜、導光板.xlsx
+++ b/Result/checksun_type/擴散膜、增亮膜、導光板.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>32.16</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>32.64</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>34.99</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>32.64</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>34.99</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>5050.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>4336.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>4336.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>5777.4</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>6847.0</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>6847</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-351.2719648777975</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>5050</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>5050.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>31.72</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>32.68</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>35.1</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>32.68</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>35.1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>5616.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>4001.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>4001.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>5931.5</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>7423.62</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>7423.62</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-411.2842611585756</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>5616</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>5616.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>31.46</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>32.74</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>35.26</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>32.74</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>35.26</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>2561.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>3993.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>3993</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>5845.1</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>7707.14</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>7707.14</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-542.9702465183082</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>2561</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2561.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>31.64</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>32.9</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>35.47</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>35.47</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>4686.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>4282.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>4282.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>5931.0</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>7956.74</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>7956.74</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-384.3798596565584</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>4686</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>4686.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>31.98</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>33.08</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>35.68</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>33.08</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>35.68</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>3769.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>4989.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>4989.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>5806.8</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>8223.9</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>8223.9</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-371.7728834377531</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>3769</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>3769.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>32.35</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>33.24</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>35.88</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>33.24</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>35.88</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>3377.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>7218.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>7218.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>6107.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>8475.5</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>8475.5</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-242.23531443097</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>3377</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>3377.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>32.85</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>33.42</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>36.09</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>33.42</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>36.09</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>5572.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>7861.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>7861.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>6235.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>9406.68</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>9406.68</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-6.530383191601686</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>5572</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>5572.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>33.15</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>33.56</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>36.32</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>33.56</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>36.32</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>4007.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>7697.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>7697.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>6678.3</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>11379.82</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>11379.82</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>95.24560369291066</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>4007</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>4007.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>33.18</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>33.67</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>36.47</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>33.67</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>36.47</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>8221.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>7579.8</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>7579.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>6844.8</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>11648.86</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>11648.86</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>404.9168133960384</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>8221</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>8221.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>33.13</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>33.78</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>36.62</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>33.78</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>36.62</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>14915.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>6624.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>6624.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>6226.0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>12140.42</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>12140.42</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>381.3429410649342</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>14915</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>14915.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>32.96999999999999</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>33.82</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>36.81</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>33.82</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>36.81</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>6591.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>4996.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>4996.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>5294.2</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>15620.94</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>15620.94</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-383.1676958746775</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>6591</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>6591.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>44.41</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>45.24</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>43.8</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>45.24</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>43.8</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>90702033.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>105746633.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>105746633</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>142323916.1</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>283181158.2</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>283181158.2</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-35659135.80271852</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>90702033</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>90702033.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>44.26000000000001</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>43.71</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>43.71</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>87525673.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>110801500.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>110801500.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>189373875.8</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>283370598.82</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>283370598.82</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-35489764.01778525</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>87525673</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>87525673.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>44.24999999999999</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>45.34</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>43.64</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>45.34</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>43.64</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>128580046.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>123016262.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>123016262.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>222414981.5</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>283171455.62</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>283171455.62</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-33639988.4672454</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>128580046</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>128580046.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>44.57</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>45.41</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>43.59</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>45.41</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>43.59</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>113653630.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>135354845.8</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>135354845.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>226837017.7</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>282518805.5</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>282518805.5</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-34194706.62835827</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>113653630</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>113653630.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>44.91</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>45.39</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>43.53</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>45.39</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>43.53</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>108271783.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>145615587.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>145615587.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>232423142.2</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>281761516.4</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>281761516.4</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-32166662.7646496</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>108271783</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>108271783.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>45.24</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>45.36</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>43.46</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>43.46</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>115976369.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>178901199.2</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>178901199.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>246879753.5</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>282984175.98</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>282984175.98</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-27544021.3963283</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>115976369</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>115976369.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>45.97</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>45.38</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>43.39</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>45.38</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>43.39</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>148599483.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>267946251.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>267946251.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>246572505.0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>282049366.78</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>282049366.78</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-20782024.32028615</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>148599483</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>148599483.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>46.44</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>45.38</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>43.32</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>45.38</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>43.32</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>190272964.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>321813700.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>321813700.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>247253736.5</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>280836529.52</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>280836529.52</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-13875146.98593</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>190272964</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>190272964.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>46.62</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>45.34</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>43.23</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>45.34</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>43.23</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>164957337.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>318319189.6</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>318319189.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>250999781.1</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>282811790.16</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>282811790.16</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-7977654.223066568</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>164957337</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>164957337.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>46.52</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>45.31</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>43.15</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>45.31</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>43.15</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>274699843.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>319230697.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>319230697.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>284091819.4</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>289666457.52</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>289666457.52</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>3444640.267562151</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>274699843</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>274699843.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>46.35</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>45.14</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>43.08</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>45.14</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>43.08</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>561201630.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>314858307.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>314858307.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>295191794.9</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>297124608.34</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>297124608.34</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>7881055.316047311</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>561201630</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>561201630.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>10.3</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>10.85</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>11.22</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>11.22</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>6305887.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>7393258.2</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>7393258.2</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>10517267.3</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>20568071.26</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>20568071.26</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-1787012.246778358</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>6305887</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>6305887.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>10.21</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>10.9</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>11.22</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>11.22</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>6730463.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>8143750.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>8143750.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>10751948.6</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>20786752.56</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>20786752.56</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-1731711.459589692</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>6730463</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>6730463.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>10.18</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>10.96</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>11.24</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>11.24</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>8188113.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>10252271.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>10252271.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>11380459.0</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>21012264.76</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>21012264.76</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-1636353.782906249</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>8188113</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>8188113.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>10.27</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>11.03</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>11.26</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>11.26</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>9675415.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>12157509.8</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>12157509.8</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>11738500.6</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>21280071.54</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>21280071.54</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-1597864.109683253</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>9675415</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>9675415.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>10.43</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>11.28</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>11.28</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>6066413.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>12520435.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>12520435.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>11198491.5</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>21364951.88</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>21364951.88</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-1645166.072590286</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>6066413</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>6066413.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>10.65</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>11.17</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>11.3</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>11.3</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>10058347.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>13641276.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>13641276.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>11429840.7</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>21624569.6</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>21624569.6</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-1267305.588436393</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>10058347</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>10058347.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>10.86</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>11.25</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>11.32</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>11.32</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>17273069.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>13360147.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>13360147</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>11469505.1</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>21758890.56</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>21758890.56</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-1109951.197200963</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>17273069</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>17273069.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>10.98</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>11.32</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>11.34</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>11.34</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>17714305.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>12508646.6</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>12508646.6</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>10959217.0</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>21599596.86</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>21599596.86</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-1618524.024107456</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>17714305</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>17714305.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>11.09</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>11.38</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>11.35</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>11.35</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>11490043.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>11319491.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>11319491.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>10877105.4</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>21406229.02</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>21406229.02</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-2334527.490255751</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>11490043</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>11490043.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>11.14</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>11.46</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>11.35</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>11.35</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>11670618.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>9876547.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>9876547.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>11219565.0</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>21593346.16</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>21593346.16</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-2607128.38867275</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>11670618</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>11670618.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>11.16</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>11.51</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>11.34</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>11.34</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>8652700.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>9218405.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>9218405</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>12205749.0</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>21688059.2</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>21688059.2</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-2922793.836815866</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>8652700</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>8652700.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>41.08</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>41.33</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>43.42</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>41.33</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>43.42</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>3859998.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>2551619.6</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>2551619.6</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>2504227.8</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>4303347.02</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>4303347.02</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-397081.4892302658</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>3859998</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>3859998.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>40.59</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>41.42</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>43.49</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>41.42</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>43.49</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>1228707.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>2137476.6</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>2137476.6</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>2436663.4</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>4380192.3</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>4380192.3</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-574047.8821928818</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>1228707</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>1228707.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>40.65</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>41.65</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>43.64</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>41.65</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>43.64</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>2517050.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>2355504.4</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>2355504.4</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>2571227.5</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>4621245.28</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>4621245.28</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-524431.2692040154</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>2517050</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>2517050.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>40.97</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>41.89</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>43.81</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>41.89</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>43.81</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>2167755.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>2418090.2</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>2418090.2</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>2814543.9</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>4962225.74</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>4962225.74</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-572857.4553197771</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>2167755</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>2167755.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>41.23</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>42.03</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>43.98</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>42.03</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>43.98</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>2984588.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>2595613.2</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>2595613.2</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>2871880.7</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>5309513.44</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>5309513.44</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-584154.0620808736</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>2984588</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>2984588.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>41.62</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>42.16</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>44.18</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>42.16</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>44.18</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>1789283.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>2456836.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>2456836</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>2936182.9</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>6060579.62</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>6060579.62</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-666947.2480938369</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>1789283</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>1789283.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>41.95</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>42.27</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>44.35</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>42.27</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>44.35</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>2318846.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>2735850.2</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>2735850.2</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>3140669.6</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>6592430.94</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>6592430.94</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-633335.2906804332</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>2318846</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>2318846.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>42.0</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>42.37</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>44.42</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>42.37</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>44.42</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>2829979.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>2786950.6</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>2786950.6</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>3354255.9</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>7219132.12</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>7219132.12</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-619437.9839941273</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>2829979</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>2829979.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>41.9</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>42.42</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>44.45</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>44.45</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>3055370.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>3210997.6</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>3210997.6</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>3403112.0</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>7407915.86</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>7407915.86</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-632226.1535853278</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>3055370</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>3055370.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>41.67999999999999</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>42.49</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>44.53</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>42.49</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>44.53</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>2290702.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>3148148.2</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>3148148.2</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>3911893.4</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>7949546.54</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>7949546.54</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-652064.497516138</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>2290702</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>2290702.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>41.3</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>44.52</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>44.52</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>3184354.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>3415529.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>3415529.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>5279318.9</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>8149957.56</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>8149957.56</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-575188.2567917202</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>3184354</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>3184354.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>58.94</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>60.02</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>60.28</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>60.02</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>60.28</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>15324.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>8129.8</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>8129.8</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>10980.9</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>12247.68</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>12247.68</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-1338.613092087846</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>15324</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>15324.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>58.14</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>60.16</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>60.27</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>60.16</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>60.27</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>4164.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>8620.4</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>8620.4</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>9990.2</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>12554.58</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>12554.58</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-2000.954018343326</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>4164</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>4164.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>57.84</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>60.34</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>60.33</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>60.34</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>60.33</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>2830.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>10935.2</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>10935.2</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>10513.0</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>12697.8</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>12697.8</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-1679.978412338893</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>2830</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>2830.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>57.64</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>60.54</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>60.4</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>60.54</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>60.4</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>8163.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>13385.4</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>13385.4</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>13276.5</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>13310.96</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>13310.96</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-1018.514031891889</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>8163</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>8163.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>57.77999999999999</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>60.74</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>60.51</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>60.74</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>60.51</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>10168.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>13264.8</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>13264.8</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>13622.6</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>13357.1</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>13357.1</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-608.5822729714582</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>10168</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>10168.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>58.02</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>60.95</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>60.64</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>60.95</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>60.64</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>17777.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>13832.0</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>13832</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>14882.0</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>13432.18</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>13432.18</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-216.0518219075748</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>17777</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>17777.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>58.48</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>61.2</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>60.81</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>60.81</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>15738.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>11360.0</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>11360</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>20395.3</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>13766.46</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>13766.46</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-462.827898176758</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>15738</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>15738.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>58.58</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>61.37</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>60.93</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>61.37</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>60.93</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>15081.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>10090.8</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>10090.8</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>21757.4</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>13684.76</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>13684.76</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-580.3712964835631</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>15081</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>15081.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>58.7</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>61.55</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>61.03</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>61.55</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>61.03</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>7560.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>13167.6</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>13167.6</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>21748.2</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>13595.16</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>13595.16</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-657.1700334760171</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>7560</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>7560.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>59.22000000000001</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>61.66</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>61.1</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>61.66</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>61.1</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>13004.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>13980.4</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>13980.4</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>21782.3</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>13721.16</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>13721.16</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>62.40927201605155</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>13004</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>13004.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>59.72000000000001</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>61.69</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>61.18</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>61.69</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>61.18</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>5417.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>15932.0</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>15932</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>21818.3</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>13767.98</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>13767.98</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>504.8650915755788</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>5417</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>5417.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>34.09</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>38.49</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>36.74</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>38.49</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>36.74</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>21966.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>23032.6</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>23032.6</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>24279.5</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>44047.4</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>44047.4</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-3295.996856766917</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>21966</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>21966.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>35.02</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>39.06</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>36.61</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>39.06</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>36.61</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>33464.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>21269.2</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>21269.2</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>25582.2</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>44082.68</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>44082.68</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-3451.276446698208</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>33464</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>33464.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>35.92999999999999</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>39.61</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>36.48</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>39.61</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>36.48</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>17834.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>17700.0</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>17700</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>23874.3</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>43670.22</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>43670.22</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-4781.773130646547</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>17834</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>17834.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>36.54</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>40.1</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>36.33</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>36.33</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>23097.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>21488.2</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>21488.2</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>25652.8</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>43784.08</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>43784.08</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-4837.062210192507</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>23097</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>23097.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>36.73</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>40.58</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>36.12</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>40.58</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>36.12</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>18802.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>24990.2</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>24990.2</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>26525.1</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>43596.94</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>43596.94</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-5307.187244894154</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>18802</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>18802.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>37.56</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>41.02</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>35.91</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>41.02</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>35.91</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>13149.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>25526.4</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>25526.4</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>29996.6</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>43534.98</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>43534.98</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-5329.073464293142</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>13149</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>13149.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>37.8</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>41.41</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>35.64</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>41.41</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>35.64</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>15618.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>29895.2</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>29895.2</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>32582.2</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>43919.34</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>43919.34</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-4564.336868281222</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>15618</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>15618.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>38.29000000000001</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>41.68</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>35.4</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>41.68</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>35.4</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>36775.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>30048.6</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>30048.6</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>33103.4</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>44116.8</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>44116.8</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-3573.379700111291</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>36775</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>36775.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>38.91</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>41.98</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>35.11</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>41.98</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>35.11</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>40607.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>29817.4</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>29817.4</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>34212.0</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>43720.24</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>43720.24</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-4296.927327721707</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>40607</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>40607.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>39.61</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>42.37</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>34.81</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>42.37</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>34.81</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>21483.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>28060.0</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>28060</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>32682.4</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>43193.14</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>43193.14</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-5587.676534032238</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>21483</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>21483.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>39.59</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>42.45</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>34.45</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>34993.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>34466.8</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>34466.8</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>34076.5</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>43412.38</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>43412.38</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-5183.044095403275</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>34993</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>34993.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>61.56</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>61.74</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>62.14</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>61.74</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>62.14</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>1408.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>1390.0</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>1390</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>1874.6</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>2505.32</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>2505.32</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-162.3915940610709</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>1408</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>1408.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>61.56</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>61.74</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>62.14</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>61.74</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>62.14</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>897.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>1319.8</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>1319.8</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>2147.2</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>2523.66</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>2523.66</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-161.590655999162</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>897</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>897.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>61.56</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>61.77</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>62.14</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>61.77</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>62.14</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>2127.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>1720.0</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>1720</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>2206.6</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>2581.7</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>2581.7</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-99.92536391075078</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>2127</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>2127.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>61.72000000000001</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>61.82</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>62.15</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>61.82</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>62.15</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>1337.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>1696.0</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>1696</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>2141.2</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>2592.12</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>2592.12</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-140.0490407876364</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>1337</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>1337.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>61.88</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>61.86</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>62.18</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>62.18</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>1181.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>1820.0</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>1820</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>2048.4</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>2632.5</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>2632.5</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-107.7239705836289</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>1181</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>1181.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>61.96</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>61.91</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>62.19</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>61.91</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>62.19</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>1057.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>2359.2</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>2359.2</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>2006.4</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>2638.44</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>2638.44</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-40.98372848563167</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>1057</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>1057.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>61.98</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>61.94</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>62.2</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>61.94</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>62.2</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>2898.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>2974.6</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>2974.6</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>2218.7</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>2658.94</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>2658.94</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>69.10889338599463</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>2898</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>2898.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>61.96</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>61.98</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>62.21</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>61.98</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>62.21</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>2007.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>2693.2</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>2693.2</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>2055.5</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>2633.78</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>2633.78</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>26.66589272453211</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>2007</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>2007.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>61.8</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>61.99</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>62.2</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>61.99</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>62.2</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>1957.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>2586.4</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>2586.4</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>1968.1</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>2647.68</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>2647.68</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>60.54496703942414</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>1957</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>1957.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>61.7</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>62.03</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>62.2</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>62.03</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>62.2</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>3877.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>2276.8</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>2276.8</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>1891.3</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>2631.9</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>2631.9</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>112.1384672378617</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>3877</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>3877.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>61.6</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>62.08</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>62.21</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>62.08</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>62.21</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>4134.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>1653.6</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>1653.6</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>1674.6</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>2583.16</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>2583.16</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-23.8757634514368</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>4134</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>4134.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>32.36</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>33.57</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>36.62</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>33.57</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>36.62</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>403535423.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>568945866.2</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>568945866.2</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>551325175.1</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>652100733.04</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>652100733.04</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>-64629376.5640012</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>403535423</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>403535423.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>32.41</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>33.75</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>36.78</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>36.78</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>363440217.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>575528949.6</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>575528949.6</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>594264436.4</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>657290966.96</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>657290966.96</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-58722927.5542357</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>363440217</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>363440217.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>32.3</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>33.94</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>36.93</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>33.94</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>36.93</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>451484020.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>575978704.8</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>575978704.8</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>641378457.8</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>656768454.26</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>656768454.26</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-43891980.91334808</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>451484020</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>451484020.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>32.09</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>34.14</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>37.07</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>34.14</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>37.07</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>569640781.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>620997783.6</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>620997783.6</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>705807978.8</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>655783883.94</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>655783883.9400001</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-30570608.14374614</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>569640781</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>569640781.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>32.14</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>34.4</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>37.2</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>37.2</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>1056628890.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>631631786.8</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>631631786.8</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>709807982.0</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>651233510.34</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>651233510.34</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-23107921.14632392</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>1056628890</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>1056628890.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>32.12</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>34.62</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>37.31</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>34.62</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>37.31</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>436450840.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>533704484.0</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>533704484</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>667262298.9</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>638216857.76</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>638216857.76</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>-63798954.21620893</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>436450840</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>436450840.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>32.35</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>34.95</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>37.46</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>37.46</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>365688993.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>612999923.2</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>612999923.2</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>705359369.1</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>635887126.76</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>635887126.76</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>-53202819.16546595</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>365688993</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>365688993.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>32.81</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>35.28</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>37.61</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>37.61</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>676579414.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>706778210.8</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>706778210.8</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>768838281.6</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>633235828.68</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>633235828.6799999</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>-28583756.22992349</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>676579414</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>676579414.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>33.39</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>35.56</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>37.76</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>37.76</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>622810797.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>790618174.0</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>790618174</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>763691422.1</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>627286041.56</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>627286041.5599999</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>-25702505.84950864</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>622810797</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>622810797.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>34.07</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>35.84</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>37.9</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>37.9</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>566992376.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>787984177.2</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>787984177.2</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>817890552.4</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>622376486.36</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>622376486.36</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>-14907563.99000478</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>566992376</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>566992376.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>34.47</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>36.09</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>38.03</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>36.09</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>38.03</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>832928036.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>800820113.8</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>800820113.8</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>848956198.4</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>625070436.22</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>625070436.22</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>7026739.630357981</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>832928036</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>832928036.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38897,11 @@
           <t>23.63</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>24.42</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>26.01</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>26.01</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38948,16 @@
           <t>69398365.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>46175655.8</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>46175655.8</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>40727993.5</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>194676121.56</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>194676121.56</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>-6011750.455637693</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>69398365</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>69398365.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>23.42</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>24.49</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>25.98</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>24.49</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>25.98</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>40606624.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>40014316.2</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>40014316.2</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>41687883.7</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>195169236.84</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>195169236.84</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>-9065902.528399438</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>40606624</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>40606624.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>23.48</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>24.64</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>25.97</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>25.97</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>33681849.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>39637812.8</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>39637812.8</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>51965661.4</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>195984000.1</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>195984000.1</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>-10020365.29204483</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>33681849</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>33681849.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>23.88</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>24.85</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>25.98</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>25.98</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>49106509.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>38566967.2</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>38566967.2</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>52615128.9</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>195992723.02</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>195992723.02</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>-10284073.15825091</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>49106509</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>49106509.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>24.26</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>25.06</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>25.98</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>25.98</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>38084932.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>35331650.4</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>35331650.4</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>52705529.4</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>195762947.24</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>195762947.24</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>-11946152.49717921</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>38084932</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>38084932.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>24.53</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>25.22</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>25.95</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>25.22</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>25.95</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>38591667.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>35280331.2</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>35280331.2</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>51774555.3</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>196053683.56</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>196053683.56</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>-12713019.99932038</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>38591667</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>38591667.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>25.11</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>25.44</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>25.96</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>25.44</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>25.96</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>38724107.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>43361451.2</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>43361451.2</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>53384515.1</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>197488634.64</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>197488634.64</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>-13408801.60954632</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>38724107</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>38724107.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>25.59</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>25.56</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>25.94</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>25.94</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>28327621.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>64293510.0</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>64293510</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>53134957.6</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>197699079.6</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>197699079.6</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>-13938079.56667101</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>28327621</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>28327621.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>25.52</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>25.58</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>25.88</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>25.88</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>32929925.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>66663290.6</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>66663290.6</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>54706545.9</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>197755621.26</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>197755621.26</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>-13082493.16375375</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>32929925</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>32929925.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>25.35</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>25.62</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>25.82</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>25.82</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>37828336.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>70079408.4</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>70079408.40000001</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>58159640.7</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>197616845.6</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>197616845.6</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>-11886098.97516645</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>37828336</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>37828336.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>25.03</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>25.62</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>25.76</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>25.76</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>78997267.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>68268779.4</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>68268779.40000001</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>64193506.3</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>197596036.22</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>197596036.22</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>-10277290.63521439</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>78997267</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>78997267.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43443,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,21 +43627,17 @@
           <t>39.02</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
+      <c r="AM101" t="n">
+        <v>39.53</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="AO101" t="inlineStr">
         <is>
           <t>39.53</t>
         </is>
       </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>40.2</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>39.53</t>
-        </is>
-      </c>
       <c r="AP101" t="inlineStr">
         <is>
           <t>-19.58</t>
@@ -44276,20 +43678,16 @@
           <t>201657416.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>252360977.6</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>252360977.6</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>282417854.9</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>423553251.3</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>423553251.3</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43704,10 @@
           <t>-36974729.3629033</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>201657416</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>201657416.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43873,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44057,11 @@
           <t>39.04000000000001</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>39.71</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>40.26</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>39.71</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>40.26</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44108,16 @@
           <t>195613562.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>255801795.6</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>255801795.6</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>285762642.3</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>457544220.78</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>457544220.78</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44134,10 @@
           <t>-35925485.46414912</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>195613562</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>195613562.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44303,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44487,11 @@
           <t>39.16</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>39.91</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>40.4</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>39.91</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>40.4</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44538,16 @@
           <t>188357162.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>277240412.8</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>277240412.8</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>297413036.7</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>528814161.92</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>528814161.92</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44564,10 @@
           <t>-32495956.77078068</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>188357162</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>188357162.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44733,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44917,11 @@
           <t>39.25</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>39.94</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>40.53</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>39.94</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>40.53</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44968,16 @@
           <t>355837208.0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>346026858.8</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>346026858.8</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>290442567.6</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>558638708.96</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>558638708.96</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44994,10 @@
           <t>-25658588.75272644</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>355837208</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>355837208.0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45163,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45347,11 @@
           <t>39.4</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>39.93</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>40.66</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>39.93</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>40.66</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45398,16 @@
           <t>320339540.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>322944767.0</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>322944767</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>273188557.9</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>613979125.7</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>613979125.7</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45424,10 @@
           <t>-32918832.62862295</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>320339540</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>320339540.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45593,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45777,11 @@
           <t>39.4</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>39.85</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>40.74</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>39.85</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>40.74</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45828,16 @@
           <t>218861506.0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>312474732.2</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>312474732.2</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>262014209.7</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>631667121.94</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>631667121.9400001</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45854,10 @@
           <t>-38311615.42888141</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>218861506</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>218861506.0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46023,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46207,11 @@
           <t>39.55</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>39.83</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>40.77</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>39.83</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>40.77</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46258,16 @@
           <t>302806648.0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>315723489.0</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>315723489</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>267936291.1</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>654424013.3</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>654424013.3</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46284,10 @@
           <t>-33774672.37821913</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>302806648</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>302806648.0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46453,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,15 +46637,11 @@
           <t>39.57000000000001</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>39.78</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>40.87</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>39.78</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>40.87</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47328,20 +46688,16 @@
           <t>532289392.0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>317585660.6</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>317585660.6</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>263274442.8</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>673739372.28</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>673739372.28</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46714,10 @@
           <t>-35081209.22090816</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>532289392</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>532289392.0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46883,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47067,11 @@
           <t>39.51000000000001</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>39.76</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>41.0</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>39.76</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>41</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47118,16 @@
           <t>240426749.0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>234858276.4</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>234858276.4</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>236240878.5</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>679732391.62</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>679732391.62</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47144,10 @@
           <t>-60282226.95257431</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>240426749</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>240426749.0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47313,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47497,11 @@
           <t>39.5</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>39.78</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>41.14</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>39.78</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>41.14</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47548,16 @@
           <t>267989366.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>223432348.8</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>223432348.8</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>270578244.9</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>693037521.34</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>693037521.34</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47574,10 @@
           <t>-62859746.71379119</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>267989366</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>267989366.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47743,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,15 +47927,11 @@
           <t>39.52</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>39.72</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>41.21</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>39.72</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>41.21</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48636,20 +47978,16 @@
           <t>235105290.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>211553687.2</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>211553687.2</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>317718579.4</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>694915339.42</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>694915339.42</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48004,10 @@
           <t>-67250064.3828941</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>235105290</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>235105290.0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
